--- a/data/trans_bre/P6903-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P6903-Clase-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 15,84</t>
+          <t>-15,41; 15,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,93; 21,99</t>
+          <t>-15,06; 20,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,81; 31,18</t>
+          <t>-9,68; 32,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 32,58</t>
+          <t>-3,53; 31,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-54,29; 88,06</t>
+          <t>-49,85; 99,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-51,81; 165,52</t>
+          <t>-49,16; 164,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-23,98; 127,31</t>
+          <t>-22,2; 135,61</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 171,44</t>
+          <t>-8,96; 156,96</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,72; 14,81</t>
+          <t>-22,68; 12,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-33,06; 7,1</t>
+          <t>-32,61; 6,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-32,92; 16,81</t>
+          <t>-31,3; 17,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 20,7</t>
+          <t>-14,61; 21,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,04; 143,91</t>
+          <t>-71,33; 101,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-87,99; 55,55</t>
+          <t>-88,24; 59,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,73; 64,03</t>
+          <t>-62,68; 63,25</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-40,77; 146,19</t>
+          <t>-46,59; 150,33</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-29,91; 20,99</t>
+          <t>-29,8; 20,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 38,28</t>
+          <t>-1,64; 38,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-15,02; 55,94</t>
+          <t>-13,06; 54,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,09; 26,53</t>
+          <t>-20,84; 25,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-80,29; 64,86</t>
+          <t>-73,93; 62,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 239,6</t>
+          <t>-8,55; 248,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-39,28; 195,13</t>
+          <t>-35,53; 187,01</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-50,15; 117,79</t>
+          <t>-53,12; 111,63</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-14,55; 15,49</t>
+          <t>-15,4; 13,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,08; 33,86</t>
+          <t>4,11; 32,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-16,07; 11,14</t>
+          <t>-17,09; 11,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-12,04; 14,99</t>
+          <t>-10,66; 13,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-40,51; 53,45</t>
+          <t>-43,69; 46,03</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,44; 190,61</t>
+          <t>15,48; 195,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-34,38; 31,28</t>
+          <t>-36,84; 30,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-26,15; 50,93</t>
+          <t>-23,63; 45,85</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 26,25</t>
+          <t>-6,86; 27,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 32,24</t>
+          <t>-9,43; 34,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,67; 25,84</t>
+          <t>-12,51; 25,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-32,71; 19,62</t>
+          <t>-29,77; 20,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,0; 108,8</t>
+          <t>-16,21; 114,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,99; 176,74</t>
+          <t>-25,79; 199,81</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-26,07; 86,99</t>
+          <t>-25,08; 82,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-58,89; 59,81</t>
+          <t>-60,62; 61,67</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1112,42 +1112,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>-0,81</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10,86</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4,57</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>-2,58%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -1160,160 +1160,59 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,31; 6,57</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,58; 18,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,82; 10,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-8,26; 12,79</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-24,54; 22,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>9,93; 90,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-16,05; 30,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-19,37; 42,26</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-0,81</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>10,86</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2,7</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>4,57</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,58%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>45,59%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>13,36%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-8,16; 8,23</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>2,61; 18,66</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-6,47; 12,36</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-8,48; 12,77</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-23,62; 30,33</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8,93; 90,77</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-15,05; 35,28</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-21,15; 41,93</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="9">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>

--- a/data/trans_bre/P6903-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P6903-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,88</t>
+          <t>12,34</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>36,89%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 15,33</t>
+          <t>-14,95; 16,02</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,06; 20,2</t>
+          <t>-14,5; 21,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 32,74</t>
+          <t>-8,76; 33,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 31,14</t>
+          <t>-6,08; 29,43</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-49,85; 99,02</t>
+          <t>-50,55; 99,27</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 164,44</t>
+          <t>-54,25; 154,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 135,61</t>
+          <t>-19,12; 146,15</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 156,96</t>
+          <t>-13,81; 140,61</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,83</t>
+          <t>6,4</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>27,94%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,68; 12,44</t>
+          <t>-22,05; 13,22</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,61; 6,38</t>
+          <t>-32,53; 9,19</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,3; 17,43</t>
+          <t>-31,87; 20,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-14,61; 21,98</t>
+          <t>-10,06; 24,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-71,33; 101,5</t>
+          <t>-68,47; 120,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-88,24; 59,55</t>
+          <t>-88,02; 68,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-62,68; 63,25</t>
+          <t>-60,3; 77,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-46,59; 150,33</t>
+          <t>-33,16; 171,47</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3,18</t>
+          <t>-0,57</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>-1,55%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-29,8; 20,15</t>
+          <t>-28,62; 24,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 38,29</t>
+          <t>-2,3; 37,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 54,26</t>
+          <t>-16,67; 53,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,84; 25,9</t>
+          <t>-22,27; 20,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-73,93; 62,46</t>
+          <t>-78,86; 76,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 248,46</t>
+          <t>-16,33; 228,77</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-35,53; 187,01</t>
+          <t>-44,1; 188,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-53,12; 111,63</t>
+          <t>-51,79; 82,33</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1,54</t>
+          <t>-0,77</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>-1,9%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-15,4; 13,56</t>
+          <t>-15,17; 14,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,11; 32,93</t>
+          <t>4,02; 33,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-17,09; 11,01</t>
+          <t>-17,64; 9,88</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 13,59</t>
+          <t>-13,82; 11,51</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,69; 46,03</t>
+          <t>-41,8; 48,66</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>15,48; 195,38</t>
+          <t>13,0; 190,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-36,84; 30,77</t>
+          <t>-37,95; 28,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 45,85</t>
+          <t>-29,19; 34,64</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,29</t>
+          <t>13,16</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-3,2%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 27,66</t>
+          <t>-7,4; 28,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 34,1</t>
+          <t>-11,7; 33,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,51; 25,24</t>
+          <t>-13,64; 22,87</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-29,77; 20,47</t>
+          <t>-4,04; 27,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,21; 114,47</t>
+          <t>-18,12; 118,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 199,81</t>
+          <t>-32,19; 171,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-25,08; 82,19</t>
+          <t>-28,14; 73,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-60,62; 61,67</t>
+          <t>-8,7; 105,86</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4,57</t>
+          <t>6,3</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>17,48%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,31; 6,57</t>
+          <t>-8,59; 6,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,58; 18,79</t>
+          <t>2,07; 19,21</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-6,82; 10,76</t>
+          <t>-6,24; 11,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 12,79</t>
+          <t>-1,65; 13,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-24,54; 22,58</t>
+          <t>-25,27; 23,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,93; 90,61</t>
+          <t>7,63; 94,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-16,05; 30,3</t>
+          <t>-13,89; 33,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,37; 42,26</t>
+          <t>-3,69; 41,82</t>
         </is>
       </c>
     </row>
